--- a/upload files/Requirements.xlsx
+++ b/upload files/Requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a8cad284f0e3288/Desktop/GitHub Repo/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{276C0676-F2F3-4C92-89CD-90EB8A517FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{276C0676-F2F3-4C92-89CD-90EB8A517FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0AAA39D-0FF3-4A71-A0DB-53899E2ED242}"/>
   <bookViews>
-    <workbookView xWindow="30340" yWindow="1680" windowWidth="27280" windowHeight="14520" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
+    <workbookView xWindow="1725" yWindow="1410" windowWidth="22995" windowHeight="13260" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="90">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -312,7 +312,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -355,13 +355,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -697,18 +697,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4207F5C1-E9B7-0644-BC5B-91118FE261AD}">
   <dimension ref="A1:F83"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.5" style="3" customWidth="1"/>
+    <col min="6" max="6" width="38.5" style="4" customWidth="1"/>
     <col min="7" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -724,11 +724,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -742,7 +742,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -753,7 +753,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -764,7 +764,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -778,7 +778,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -792,7 +792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -803,7 +803,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -817,7 +817,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -828,7 +828,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -839,7 +839,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -853,7 +853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -864,7 +864,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -877,8 +877,11 @@
       <c r="D13" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="F13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -889,7 +892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -903,7 +906,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
@@ -917,7 +920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -934,7 +937,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -948,7 +951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -959,7 +962,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -970,7 +973,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -984,7 +987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -998,7 +1001,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
@@ -1012,7 +1015,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
@@ -1026,7 +1029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
@@ -1040,7 +1043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
@@ -1051,7 +1054,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
@@ -1065,7 +1068,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -1079,7 +1082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
@@ -1093,7 +1096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
@@ -1107,7 +1110,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -1121,7 +1124,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -1135,7 +1138,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
@@ -1149,7 +1152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -1163,7 +1166,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
@@ -1177,7 +1180,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
@@ -1191,7 +1194,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>43</v>
       </c>
@@ -1205,7 +1208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
@@ -1216,7 +1219,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>45</v>
       </c>
@@ -1230,7 +1233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
@@ -1244,7 +1247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>47</v>
       </c>
@@ -1258,7 +1261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>48</v>
       </c>
@@ -1272,7 +1275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>49</v>
       </c>
@@ -1283,7 +1286,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
@@ -1297,7 +1300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
@@ -1311,7 +1314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
@@ -1325,7 +1328,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
@@ -1339,7 +1342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>54</v>
       </c>
@@ -1353,7 +1356,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
@@ -1367,7 +1370,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
@@ -1381,7 +1384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>57</v>
       </c>
@@ -1395,7 +1398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>58</v>
       </c>
@@ -1409,7 +1412,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>59</v>
       </c>
@@ -1423,7 +1426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>60</v>
       </c>
@@ -1437,7 +1440,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>61</v>
       </c>
@@ -1451,7 +1454,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>62</v>
       </c>
@@ -1465,7 +1468,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>63</v>
       </c>
@@ -1479,7 +1482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>64</v>
       </c>
@@ -1493,7 +1496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>65</v>
       </c>
@@ -1507,7 +1510,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>66</v>
       </c>
@@ -1521,7 +1524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>67</v>
       </c>
@@ -1535,7 +1538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>68</v>
       </c>
@@ -1549,7 +1552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>69</v>
       </c>
@@ -1563,7 +1566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>70</v>
       </c>
@@ -1577,7 +1580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>71</v>
       </c>
@@ -1591,7 +1594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>72</v>
       </c>
@@ -1605,7 +1608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>73</v>
       </c>
@@ -1619,7 +1622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>74</v>
       </c>
@@ -1630,7 +1633,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>75</v>
       </c>
@@ -1644,7 +1647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>76</v>
       </c>
@@ -1658,7 +1661,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>77</v>
       </c>
@@ -1672,7 +1675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>78</v>
       </c>
@@ -1686,7 +1689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>79</v>
       </c>
@@ -1700,7 +1703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>80</v>
       </c>
@@ -1714,7 +1717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>81</v>
       </c>
@@ -1728,7 +1731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>82</v>
       </c>
@@ -1742,7 +1745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>83</v>
       </c>
@@ -1756,7 +1759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>84</v>
       </c>
@@ -1770,7 +1773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>85</v>
       </c>
@@ -1784,7 +1787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>86</v>
       </c>
@@ -1798,7 +1801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>87</v>
       </c>
@@ -1812,7 +1815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>88</v>
       </c>
@@ -1826,7 +1829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>89</v>
       </c>
@@ -2029,6 +2032,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2037,22 +2048,39 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45774086-89DE-416A-B623-AE484A1E6796}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45774086-89DE-416A-B623-AE484A1E6796}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+    <ds:schemaRef ds:uri="b0d30a24-05e2-4154-8fed-e579ddd987b0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/upload files/Requirements.xlsx
+++ b/upload files/Requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a8cad284f0e3288/Desktop/GitHub Repo/CrewOps360/upload files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{276C0676-F2F3-4C92-89CD-90EB8A517FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0AAA39D-0FF3-4A71-A0DB-53899E2ED242}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3DF1C74-39C4-4079-9990-12CC95E06AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1725" yWindow="1410" windowWidth="22995" windowHeight="13260" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
+    <workbookView xWindow="30340" yWindow="1680" windowWidth="27280" windowHeight="14520" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -312,7 +312,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -347,7 +347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -355,13 +355,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -697,18 +696,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4207F5C1-E9B7-0644-BC5B-91118FE261AD}">
   <dimension ref="A1:F83"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="11.125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.5" style="4" customWidth="1"/>
+    <col min="6" max="6" width="38.5" style="3" customWidth="1"/>
     <col min="7" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -724,11 +723,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -742,7 +741,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -753,7 +752,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -764,7 +763,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -778,7 +777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -792,7 +791,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -803,7 +802,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -817,7 +816,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -828,7 +827,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -839,7 +838,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -853,7 +852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -864,7 +863,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -877,11 +876,8 @@
       <c r="D13" s="1">
         <v>5</v>
       </c>
-      <c r="F13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -892,7 +888,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -906,7 +902,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
@@ -920,7 +916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -933,11 +929,11 @@
       <c r="D17" s="1">
         <v>5</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -951,7 +947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -962,7 +958,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -973,7 +969,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -987,7 +983,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -1001,7 +997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
@@ -1015,7 +1011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
@@ -1029,7 +1025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
@@ -1043,7 +1039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
@@ -1054,7 +1050,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
@@ -1068,7 +1064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -1082,7 +1078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
@@ -1096,7 +1092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
@@ -1110,7 +1106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -1124,7 +1120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -1138,7 +1134,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
@@ -1152,7 +1148,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -1166,7 +1162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
@@ -1180,7 +1176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
@@ -1194,7 +1190,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
         <v>43</v>
       </c>
@@ -1208,7 +1204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
@@ -1219,7 +1215,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
         <v>45</v>
       </c>
@@ -1233,7 +1229,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
@@ -1247,21 +1243,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B41" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C41" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D41" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
         <v>48</v>
       </c>
@@ -1275,7 +1271,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
         <v>49</v>
       </c>
@@ -1286,7 +1282,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4">
       <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
@@ -1300,7 +1296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
@@ -1314,7 +1310,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4">
       <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
@@ -1328,7 +1324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
@@ -1342,7 +1338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4">
       <c r="A48" s="1" t="s">
         <v>54</v>
       </c>
@@ -1356,7 +1352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
@@ -1370,7 +1366,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4">
       <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
@@ -1384,7 +1380,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4">
       <c r="A51" s="1" t="s">
         <v>57</v>
       </c>
@@ -1398,7 +1394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4">
       <c r="A52" s="1" t="s">
         <v>58</v>
       </c>
@@ -1412,7 +1408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4">
       <c r="A53" s="1" t="s">
         <v>59</v>
       </c>
@@ -1426,7 +1422,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4">
       <c r="A54" s="1" t="s">
         <v>60</v>
       </c>
@@ -1440,7 +1436,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4">
       <c r="A55" s="1" t="s">
         <v>61</v>
       </c>
@@ -1454,7 +1450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4">
       <c r="A56" s="1" t="s">
         <v>62</v>
       </c>
@@ -1468,7 +1464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4">
       <c r="A57" s="1" t="s">
         <v>63</v>
       </c>
@@ -1482,7 +1478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4">
       <c r="A58" s="1" t="s">
         <v>64</v>
       </c>
@@ -1496,7 +1492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4">
       <c r="A59" s="1" t="s">
         <v>65</v>
       </c>
@@ -1510,7 +1506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4">
       <c r="A60" s="1" t="s">
         <v>66</v>
       </c>
@@ -1524,7 +1520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4">
       <c r="A61" s="1" t="s">
         <v>67</v>
       </c>
@@ -1538,7 +1534,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4">
       <c r="A62" s="1" t="s">
         <v>68</v>
       </c>
@@ -1552,7 +1548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4">
       <c r="A63" s="1" t="s">
         <v>69</v>
       </c>
@@ -1566,7 +1562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4">
       <c r="A64" s="1" t="s">
         <v>70</v>
       </c>
@@ -1580,7 +1576,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4">
       <c r="A65" s="1" t="s">
         <v>71</v>
       </c>
@@ -1594,7 +1590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4">
       <c r="A66" s="1" t="s">
         <v>72</v>
       </c>
@@ -1608,7 +1604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4">
       <c r="A67" s="1" t="s">
         <v>73</v>
       </c>
@@ -1622,7 +1618,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4">
       <c r="A68" s="1" t="s">
         <v>74</v>
       </c>
@@ -1633,7 +1629,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4">
       <c r="A69" s="1" t="s">
         <v>75</v>
       </c>
@@ -1647,7 +1643,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4">
       <c r="A70" s="1" t="s">
         <v>76</v>
       </c>
@@ -1661,7 +1657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4">
       <c r="A71" s="1" t="s">
         <v>77</v>
       </c>
@@ -1675,7 +1671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4">
       <c r="A72" s="1" t="s">
         <v>78</v>
       </c>
@@ -1689,7 +1685,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4">
       <c r="A73" s="1" t="s">
         <v>79</v>
       </c>
@@ -1703,7 +1699,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4">
       <c r="A74" s="1" t="s">
         <v>80</v>
       </c>
@@ -1717,7 +1713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4">
       <c r="A75" s="1" t="s">
         <v>81</v>
       </c>
@@ -1731,7 +1727,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4">
       <c r="A76" s="1" t="s">
         <v>82</v>
       </c>
@@ -1745,7 +1741,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4">
       <c r="A77" s="1" t="s">
         <v>83</v>
       </c>
@@ -1759,7 +1755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4">
       <c r="A78" s="1" t="s">
         <v>84</v>
       </c>
@@ -1773,7 +1769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4">
       <c r="A79" s="1" t="s">
         <v>85</v>
       </c>
@@ -1787,7 +1783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4">
       <c r="A80" s="1" t="s">
         <v>86</v>
       </c>
@@ -1801,7 +1797,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4">
       <c r="A81" s="1" t="s">
         <v>87</v>
       </c>
@@ -1815,7 +1811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4">
       <c r="A82" s="1" t="s">
         <v>88</v>
       </c>
@@ -1829,7 +1825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4">
       <c r="A83" s="1" t="s">
         <v>89</v>
       </c>
@@ -2032,14 +2028,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2048,39 +2036,22 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45774086-89DE-416A-B623-AE484A1E6796}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-    <ds:schemaRef ds:uri="b0d30a24-05e2-4154-8fed-e579ddd987b0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45774086-89DE-416A-B623-AE484A1E6796}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}"/>
 </file>
--- a/upload files/Requirements.xlsx
+++ b/upload files/Requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3DF1C74-39C4-4079-9990-12CC95E06AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077E2C03-9995-6545-AA64-C70A0D969141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30340" yWindow="1680" windowWidth="27280" windowHeight="14520" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="98">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -306,13 +306,37 @@
   </si>
   <si>
     <t>Phelan</t>
+  </si>
+  <si>
+    <t>Gil.Lewis@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Mike.Hourihan@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Laura.Moreau@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Erica.Puopolo@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Scott.McKinnon@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>beth.mee@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Francis.McNulty@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>James.Boomhower@bostonmedflight.org</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -696,18 +720,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4207F5C1-E9B7-0644-BC5B-91118FE261AD}">
   <dimension ref="A1:F83"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.5" style="3" customWidth="1"/>
     <col min="7" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -727,7 +751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -741,7 +765,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -752,7 +776,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -763,7 +787,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -777,7 +801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -791,7 +815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -802,7 +826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -816,7 +840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -827,7 +851,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -838,7 +862,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -852,7 +876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -863,7 +887,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -876,8 +900,11 @@
       <c r="D13" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="F13" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -888,7 +915,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -901,8 +928,11 @@
       <c r="D15" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="F15" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
@@ -915,8 +945,11 @@
       <c r="D16" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.75">
+      <c r="F16" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -933,7 +966,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -946,8 +979,11 @@
       <c r="D18" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="F18" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -958,7 +994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -969,7 +1005,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -982,8 +1018,11 @@
       <c r="D21" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="F21" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -996,8 +1035,11 @@
       <c r="D22" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="F22" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
@@ -1010,8 +1052,11 @@
       <c r="D23" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="F23" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
@@ -1024,8 +1069,11 @@
       <c r="D24" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="F24" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
@@ -1039,7 +1087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
@@ -1050,7 +1098,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
@@ -1064,7 +1112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -1078,7 +1126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
@@ -1092,7 +1140,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
@@ -1106,7 +1154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -1120,7 +1168,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -1134,7 +1182,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
@@ -1148,7 +1196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -1162,7 +1210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
@@ -1176,7 +1224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
@@ -1190,7 +1238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>43</v>
       </c>
@@ -1204,7 +1252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
@@ -1215,7 +1263,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>45</v>
       </c>
@@ -1229,7 +1277,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
@@ -1243,7 +1291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>47</v>
       </c>
@@ -1257,7 +1305,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>48</v>
       </c>
@@ -1271,7 +1319,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>49</v>
       </c>
@@ -1282,7 +1330,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
@@ -1296,7 +1344,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
@@ -1310,7 +1358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
@@ -1324,7 +1372,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
@@ -1338,7 +1386,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>54</v>
       </c>
@@ -1352,7 +1400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
@@ -1366,7 +1414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
@@ -1380,7 +1428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>57</v>
       </c>
@@ -1394,7 +1442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>58</v>
       </c>
@@ -1408,7 +1456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>59</v>
       </c>
@@ -1422,7 +1470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>60</v>
       </c>
@@ -1436,7 +1484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>61</v>
       </c>
@@ -1450,7 +1498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>62</v>
       </c>
@@ -1464,7 +1512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>63</v>
       </c>
@@ -1478,7 +1526,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>64</v>
       </c>
@@ -1492,7 +1540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>65</v>
       </c>
@@ -1506,7 +1554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>66</v>
       </c>
@@ -1520,7 +1568,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>67</v>
       </c>
@@ -1534,7 +1582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>68</v>
       </c>
@@ -1548,7 +1596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>69</v>
       </c>
@@ -1562,7 +1610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>70</v>
       </c>
@@ -1576,7 +1624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>71</v>
       </c>
@@ -1590,7 +1638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>72</v>
       </c>
@@ -1604,7 +1652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>73</v>
       </c>
@@ -1618,7 +1666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>74</v>
       </c>
@@ -1629,7 +1677,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>75</v>
       </c>
@@ -1643,7 +1691,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>76</v>
       </c>
@@ -1657,7 +1705,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>77</v>
       </c>
@@ -1671,7 +1719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>78</v>
       </c>
@@ -1685,7 +1733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>79</v>
       </c>
@@ -1699,7 +1747,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>80</v>
       </c>
@@ -1713,7 +1761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>81</v>
       </c>
@@ -1727,7 +1775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>82</v>
       </c>
@@ -1741,7 +1789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>83</v>
       </c>
@@ -1755,7 +1803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>84</v>
       </c>
@@ -1769,7 +1817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>85</v>
       </c>
@@ -1783,7 +1831,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>86</v>
       </c>
@@ -1797,7 +1845,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>87</v>
       </c>
@@ -1811,7 +1859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>88</v>
       </c>
@@ -1825,7 +1873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>89</v>
       </c>
@@ -1845,6 +1893,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -2027,15 +2084,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2045,13 +2093,38 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45774086-89DE-416A-B623-AE484A1E6796}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45774086-89DE-416A-B623-AE484A1E6796}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+    <ds:schemaRef ds:uri="b0d30a24-05e2-4154-8fed-e579ddd987b0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/upload files/Requirements.xlsx
+++ b/upload files/Requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a8cad284f0e3288/Desktop/GitHub Repo/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077E2C03-9995-6545-AA64-C70A0D969141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{077E2C03-9995-6545-AA64-C70A0D969141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCECC536-ABE7-4875-AEDF-5548FD073925}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
+    <workbookView xWindow="29490" yWindow="1155" windowWidth="22995" windowHeight="13260" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -720,18 +720,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4207F5C1-E9B7-0644-BC5B-91118FE261AD}">
   <dimension ref="A1:F83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.5" style="3" customWidth="1"/>
     <col min="7" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -751,7 +751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -765,7 +765,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -776,7 +776,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -787,7 +787,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -801,7 +801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -815,7 +815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -826,7 +826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -840,7 +840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -851,7 +851,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -862,7 +862,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -876,7 +876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -887,7 +887,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -904,7 +904,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -915,7 +915,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -932,7 +932,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
@@ -940,7 +940,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
@@ -949,7 +949,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -966,7 +966,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -983,7 +983,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -994,7 +994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>43</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>45</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
@@ -1291,7 +1291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>47</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>48</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>49</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>54</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>57</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>58</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>59</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>60</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>61</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>62</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>63</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>64</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>65</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>66</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>67</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>68</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>69</v>
       </c>
@@ -1610,7 +1610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>70</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>71</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>72</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>73</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>74</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>75</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>76</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>77</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>78</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>79</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>80</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>81</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>82</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>83</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>84</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>85</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>86</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>87</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>88</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>89</v>
       </c>
@@ -1893,15 +1893,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -2084,6 +2075,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2093,14 +2093,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45774086-89DE-416A-B623-AE484A1E6796}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2119,6 +2111,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}">
   <ds:schemaRefs>

--- a/upload files/Requirements.xlsx
+++ b/upload files/Requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a8cad284f0e3288/Desktop/GitHub Repo/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{077E2C03-9995-6545-AA64-C70A0D969141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCECC536-ABE7-4875-AEDF-5548FD073925}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{077E2C03-9995-6545-AA64-C70A0D969141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E50E092-8CAC-4A5C-80E2-29F80A7D92FC}"/>
   <bookViews>
     <workbookView xWindow="29490" yWindow="1155" windowWidth="22995" windowHeight="13260" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
   </bookViews>
@@ -1030,7 +1030,7 @@
         <v>4</v>
       </c>
       <c r="C22" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="1">
         <v>3</v>

--- a/upload files/Requirements.xlsx
+++ b/upload files/Requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a8cad284f0e3288/Desktop/GitHub Repo/CrewOps360/upload files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{077E2C03-9995-6545-AA64-C70A0D969141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E50E092-8CAC-4A5C-80E2-29F80A7D92FC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDB9257-7C0A-D241-981D-4BAA701E88F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29490" yWindow="1155" windowWidth="22995" windowHeight="13260" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -720,18 +720,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4207F5C1-E9B7-0644-BC5B-91118FE261AD}">
   <dimension ref="A1:F83"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.5" style="3" customWidth="1"/>
     <col min="7" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -751,7 +751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -765,7 +765,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -776,7 +776,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -787,7 +787,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -798,10 +798,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -815,7 +815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -826,7 +826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -840,7 +840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -851,7 +851,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -862,7 +862,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -876,7 +876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -887,7 +887,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -904,7 +904,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -915,7 +915,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -932,7 +932,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
@@ -949,7 +949,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -966,7 +966,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -983,7 +983,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -994,7 +994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>43</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>45</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
@@ -1291,7 +1291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>47</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>48</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>49</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>54</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>57</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>58</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>59</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>60</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>61</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>62</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>63</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>64</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>65</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>66</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>67</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>68</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>69</v>
       </c>
@@ -1610,7 +1610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>70</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>71</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>72</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>73</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>74</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>75</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>76</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>77</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>78</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>79</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>80</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>81</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>82</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>83</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>84</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>85</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>86</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>87</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>88</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>89</v>
       </c>
@@ -1893,6 +1893,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -2075,15 +2084,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2093,6 +2093,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45774086-89DE-416A-B623-AE484A1E6796}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2111,14 +2119,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}">
   <ds:schemaRefs>

--- a/upload files/Requirements.xlsx
+++ b/upload files/Requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDB9257-7C0A-D241-981D-4BAA701E88F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7E8E30-A633-744B-AAE6-1C21826683A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
   </bookViews>
@@ -792,7 +792,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -1893,15 +1893,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -2084,6 +2075,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2093,14 +2093,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45774086-89DE-416A-B623-AE484A1E6796}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2119,6 +2111,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}">
   <ds:schemaRefs>

--- a/upload files/Requirements.xlsx
+++ b/upload files/Requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7E8E30-A633-744B-AAE6-1C21826683A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A21E3C0-67E8-3B41-AA38-90E3C1BF9E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="99">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t>James.Boomhower@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Michael.Pepin@bostonmedflight.org</t>
   </si>
 </sst>
 </file>
@@ -875,6 +878,9 @@
       <c r="D11" s="1">
         <v>5</v>
       </c>
+      <c r="F11" s="3" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
@@ -1893,6 +1899,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -2075,24 +2098,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45774086-89DE-416A-B623-AE484A1E6796}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2109,22 +2133,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/upload files/Requirements.xlsx
+++ b/upload files/Requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A21E3C0-67E8-3B41-AA38-90E3C1BF9E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79886FFC-DFAD-E344-91A8-055215C6EE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
   </bookViews>
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>90</v>
@@ -1899,23 +1899,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -2098,25 +2081,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45774086-89DE-416A-B623-AE484A1E6796}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2133,4 +2115,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/upload files/Requirements.xlsx
+++ b/upload files/Requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79886FFC-DFAD-E344-91A8-055215C6EE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B05218-8EFA-B947-9097-40B884177F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
   </bookViews>
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>90</v>
@@ -1899,6 +1899,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -2081,15 +2090,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2099,6 +2099,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45774086-89DE-416A-B623-AE484A1E6796}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2117,14 +2125,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}">
   <ds:schemaRefs>

--- a/upload files/Requirements.xlsx
+++ b/upload files/Requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B05218-8EFA-B947-9097-40B884177F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04C659C-86EB-8445-BD14-98CBB236BDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="98">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -171,9 +171,6 @@
   </si>
   <si>
     <t>Steckevicz</t>
-  </si>
-  <si>
-    <t>DiNardo</t>
   </si>
   <si>
     <t>McGrath</t>
@@ -722,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4207F5C1-E9B7-0644-BC5B-91118FE261AD}">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -879,7 +876,7 @@
         <v>5</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -907,7 +904,7 @@
         <v>5</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -935,7 +932,7 @@
         <v>5</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -952,7 +949,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -986,7 +983,7 @@
         <v>5</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -1025,7 +1022,7 @@
         <v>5</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -1042,7 +1039,7 @@
         <v>3</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1059,7 +1056,7 @@
         <v>5</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -1076,7 +1073,7 @@
         <v>5</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -1287,53 +1284,53 @@
       <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B40" s="1">
-        <v>6</v>
+      <c r="B40" s="2">
+        <v>3</v>
       </c>
       <c r="C40" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D40" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="2">
-        <v>3</v>
+      <c r="B41" s="1">
+        <v>6</v>
       </c>
       <c r="C41" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D41" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="1">
-        <v>6</v>
-      </c>
-      <c r="C42" s="1">
-        <v>7</v>
-      </c>
-      <c r="D42" s="1">
-        <v>5</v>
+      <c r="C42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>7</v>
+      <c r="B43" s="1">
+        <v>6</v>
+      </c>
+      <c r="C43" s="1">
+        <v>7</v>
+      </c>
+      <c r="D43" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -1662,25 +1659,25 @@
       <c r="A67" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B67" s="1">
-        <v>6</v>
-      </c>
-      <c r="C67" s="1">
-        <v>7</v>
-      </c>
-      <c r="D67" s="1">
-        <v>5</v>
+      <c r="C67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>7</v>
+      <c r="B68" s="1">
+        <v>6</v>
+      </c>
+      <c r="C68" s="1">
+        <v>8</v>
+      </c>
+      <c r="D68" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -1876,20 +1873,6 @@
         <v>8</v>
       </c>
       <c r="D82" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B83" s="1">
-        <v>6</v>
-      </c>
-      <c r="C83" s="1">
-        <v>8</v>
-      </c>
-      <c r="D83" s="1">
         <v>5</v>
       </c>
     </row>
@@ -1899,15 +1882,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -2090,6 +2064,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2099,14 +2082,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45774086-89DE-416A-B623-AE484A1E6796}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2125,6 +2100,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}">
   <ds:schemaRefs>

--- a/upload files/Requirements.xlsx
+++ b/upload files/Requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04C659C-86EB-8445-BD14-98CBB236BDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F3E5FC-27DD-0048-9BCA-8A3BB1C5D369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
   </bookViews>
@@ -176,9 +176,6 @@
     <t>McGrath</t>
   </si>
   <si>
-    <t>Noland</t>
-  </si>
-  <si>
     <t>Murphy</t>
   </si>
   <si>
@@ -330,6 +327,9 @@
   </si>
   <si>
     <t>Michael.Pepin@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Seyoum</t>
   </si>
 </sst>
 </file>
@@ -876,7 +876,7 @@
         <v>5</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -904,7 +904,7 @@
         <v>5</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -932,7 +932,7 @@
         <v>5</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -949,7 +949,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -983,7 +983,7 @@
         <v>5</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -1022,7 +1022,7 @@
         <v>5</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -1039,7 +1039,7 @@
         <v>3</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1056,7 +1056,7 @@
         <v>5</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -1073,7 +1073,7 @@
         <v>5</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -1282,7 +1282,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="B40" s="2">
         <v>3</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" s="1">
         <v>6</v>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>7</v>
@@ -1321,7 +1321,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B43" s="1">
         <v>6</v>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B44" s="1">
         <v>6</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45" s="1">
         <v>6</v>
@@ -1363,7 +1363,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B46" s="1">
         <v>6</v>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" s="1">
         <v>6</v>
@@ -1391,7 +1391,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" s="1">
         <v>6</v>
@@ -1405,7 +1405,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" s="1">
         <v>6</v>
@@ -1419,7 +1419,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B50" s="1">
         <v>6</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" s="1">
         <v>6</v>
@@ -1447,7 +1447,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B52" s="1">
         <v>6</v>
@@ -1461,7 +1461,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B53" s="1">
         <v>6</v>
@@ -1475,7 +1475,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B54" s="1">
         <v>6</v>
@@ -1489,7 +1489,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B55" s="1">
         <v>6</v>
@@ -1503,7 +1503,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B56" s="1">
         <v>6</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B57" s="1">
         <v>6</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B58" s="1">
         <v>6</v>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B59" s="1">
         <v>6</v>
@@ -1559,7 +1559,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B60" s="1">
         <v>6</v>
@@ -1573,7 +1573,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B61" s="1">
         <v>6</v>
@@ -1587,7 +1587,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B62" s="1">
         <v>6</v>
@@ -1601,7 +1601,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B63" s="1">
         <v>6</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B64" s="1">
         <v>6</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B65" s="1">
         <v>6</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B66" s="1">
         <v>6</v>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>7</v>
@@ -1668,7 +1668,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B68" s="1">
         <v>6</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B69" s="1">
         <v>6</v>
@@ -1696,7 +1696,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B70" s="1">
         <v>6</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B71" s="1">
         <v>6</v>
@@ -1724,7 +1724,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B72" s="1">
         <v>6</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B73" s="1">
         <v>6</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B74" s="1">
         <v>6</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B75" s="1">
         <v>6</v>
@@ -1780,7 +1780,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B76" s="1">
         <v>6</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B77" s="1">
         <v>6</v>
@@ -1808,7 +1808,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B78" s="1">
         <v>6</v>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B79" s="1">
         <v>6</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B80" s="1">
         <v>6</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B81" s="1">
         <v>6</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B82" s="1">
         <v>6</v>
@@ -2065,20 +2065,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2101,14 +2101,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2116,4 +2108,12 @@
     <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/upload files/Requirements.xlsx
+++ b/upload files/Requirements.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F3E5FC-27DD-0048-9BCA-8A3BB1C5D369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A8B3BF-EE98-2A4F-9A00-4785F06BA3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{10D55376-794F-6145-963B-6A2FF77FD7A3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="106">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -330,6 +330,30 @@
   </si>
   <si>
     <t>Seyoum</t>
+  </si>
+  <si>
+    <t>Katelin.Phillips@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Ryan.Phillips@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Philip.Boege@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Robert.Johnson@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Catie.Graham@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Cayleigh.Montano@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Michael.Gittleson@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Matthew.Gibbs@bostonmedflight.org</t>
   </si>
 </sst>
 </file>
@@ -1089,6 +1113,9 @@
       <c r="D25" s="1">
         <v>5</v>
       </c>
+      <c r="F25" s="3" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
@@ -1114,6 +1141,9 @@
       <c r="D27" s="1">
         <v>5</v>
       </c>
+      <c r="F27" s="3" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
@@ -1128,6 +1158,9 @@
       <c r="D28" s="1">
         <v>5</v>
       </c>
+      <c r="F28" s="3" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -1142,6 +1175,9 @@
       <c r="D29" s="1">
         <v>5</v>
       </c>
+      <c r="F29" s="3" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -1156,6 +1192,9 @@
       <c r="D30" s="1">
         <v>5</v>
       </c>
+      <c r="F30" s="3" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
@@ -1170,6 +1209,9 @@
       <c r="D31" s="1">
         <v>5</v>
       </c>
+      <c r="F31" s="3" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
@@ -1184,8 +1226,11 @@
       <c r="D32" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F32" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
@@ -1198,8 +1243,11 @@
       <c r="D33" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F33" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -1213,7 +1261,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
@@ -1227,7 +1275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
@@ -1241,7 +1289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>43</v>
       </c>
@@ -1255,7 +1303,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
@@ -1266,7 +1314,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>45</v>
       </c>
@@ -1280,7 +1328,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>97</v>
       </c>
@@ -1294,7 +1342,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>46</v>
       </c>
@@ -1308,7 +1356,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>47</v>
       </c>
@@ -1319,7 +1367,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>48</v>
       </c>
@@ -1333,7 +1381,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>49</v>
       </c>
@@ -1347,7 +1395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>50</v>
       </c>
@@ -1361,7 +1409,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>51</v>
       </c>
@@ -1375,7 +1423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>52</v>
       </c>
@@ -1389,7 +1437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>53</v>
       </c>
@@ -1882,6 +1930,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -2064,14 +2120,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2082,6 +2130,16 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45774086-89DE-416A-B623-AE484A1E6796}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2100,16 +2158,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E8E94FF-6E53-4E14-A123-F68683276D30}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FC3EAF2-EF9F-4ED7-9C58-0B29683A52D2}">
   <ds:schemaRefs>

--- a/upload files/Requirements.xlsx
+++ b/upload files/Requirements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACE7ED8-0C99-4A49-9663-9548FBDCFA52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3311A13-BA45-4845-B0E3-E707BABA3822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="14720" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -371,6 +371,66 @@
   </si>
   <si>
     <t>Jeffrey.Sturtevant@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Kaitlyn.Sheary@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Jamie.Eastman@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Zachary.Charest@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Carl.Rabickow@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Greg.Worsman@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Scott.Marcosa@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Doran.Timm@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Domenic.Carchia@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Mary.Kraby@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Nicole.Saraceno@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Liz.Machado@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Aisling.Sammon@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Widmac.Laterion@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Mathew.Boutilier@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Luke.Fielding@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Benjamin.Romano@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Harry.Creekmuir@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Robert.O'Donnell@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Connor.Bach@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Aaron.Shelanskas@bostonmedflight.org</t>
   </si>
 </sst>
 </file>
@@ -1423,8 +1483,11 @@
       <c r="D48" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F48" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>71</v>
       </c>
@@ -1437,8 +1500,11 @@
       <c r="D49" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F49" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>72</v>
       </c>
@@ -1451,8 +1517,11 @@
       <c r="D50" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F50" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>73</v>
       </c>
@@ -1465,8 +1534,11 @@
       <c r="D51" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F51" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>74</v>
       </c>
@@ -1479,8 +1551,11 @@
       <c r="D52" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F52" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>75</v>
       </c>
@@ -1493,8 +1568,11 @@
       <c r="D53" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F53" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>76</v>
       </c>
@@ -1507,8 +1585,11 @@
       <c r="D54" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F54" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>77</v>
       </c>
@@ -1521,8 +1602,11 @@
       <c r="D55" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F55" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>78</v>
       </c>
@@ -1535,8 +1619,11 @@
       <c r="D56" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F56" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>79</v>
       </c>
@@ -1549,8 +1636,11 @@
       <c r="D57" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F57" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>80</v>
       </c>
@@ -1563,8 +1653,11 @@
       <c r="D58" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F58" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>81</v>
       </c>
@@ -1577,8 +1670,11 @@
       <c r="D59" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F59" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>82</v>
       </c>
@@ -1591,22 +1687,16 @@
       <c r="D60" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F60" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B61" s="1">
-        <v>6</v>
-      </c>
-      <c r="C61" s="1">
-        <v>7</v>
-      </c>
-      <c r="D61" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>84</v>
       </c>
@@ -1619,8 +1709,11 @@
       <c r="D62" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F62" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>85</v>
       </c>
@@ -1633,8 +1726,11 @@
       <c r="D63" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F63" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>86</v>
       </c>
@@ -1647,8 +1743,11 @@
       <c r="D64" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F64" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>87</v>
       </c>
@@ -1661,8 +1760,11 @@
       <c r="D65" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F65" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>88</v>
       </c>
@@ -1675,13 +1777,16 @@
       <c r="D66" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F66" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>90</v>
       </c>
@@ -1694,8 +1799,11 @@
       <c r="D68" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F68" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>91</v>
       </c>
@@ -1708,8 +1816,11 @@
       <c r="D69" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F69" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>92</v>
       </c>
@@ -1723,7 +1834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>93</v>
       </c>
@@ -1737,7 +1848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>94</v>
       </c>
@@ -1751,7 +1862,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>95</v>
       </c>
@@ -1765,7 +1876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>96</v>
       </c>
@@ -1779,7 +1890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>97</v>
       </c>
@@ -1793,7 +1904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>98</v>
       </c>
@@ -1807,7 +1918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>99</v>
       </c>
@@ -1821,7 +1932,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>100</v>
       </c>
@@ -1835,7 +1946,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>101</v>
       </c>
@@ -1849,7 +1960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>102</v>
       </c>

--- a/upload files/Requirements.xlsx
+++ b/upload files/Requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3311A13-BA45-4845-B0E3-E707BABA3822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A22A4713-A78B-FD41-A609-C0DB4029FF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="14720" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -431,6 +431,45 @@
   </si>
   <si>
     <t>Aaron.Shelanskas@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Nora.Young@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Michele.Lane@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Max.Cowart@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Brian.Walker@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Marc.Wyzansky@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Victoria.Sacco@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Travis.Clark@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Leah.Kelley@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Morgan.Payton@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Kyle.Ravenelle@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Brendan.O'Flaherty@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Kyle.Vanderkooi@bostonmedflight.org</t>
+  </si>
+  <si>
+    <t>Ryan.Phelan@bostonmedflight.org</t>
   </si>
 </sst>
 </file>
@@ -1833,6 +1872,9 @@
       <c r="D70" s="1">
         <v>5</v>
       </c>
+      <c r="F70" s="3" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
@@ -1847,6 +1889,9 @@
       <c r="D71" s="1">
         <v>5</v>
       </c>
+      <c r="F71" s="3" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
@@ -1861,6 +1906,9 @@
       <c r="D72" s="1">
         <v>5</v>
       </c>
+      <c r="F72" s="3" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
@@ -1875,6 +1923,9 @@
       <c r="D73" s="1">
         <v>5</v>
       </c>
+      <c r="F73" s="3" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
@@ -1889,6 +1940,9 @@
       <c r="D74" s="1">
         <v>5</v>
       </c>
+      <c r="F74" s="3" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
@@ -1903,6 +1957,9 @@
       <c r="D75" s="1">
         <v>5</v>
       </c>
+      <c r="F75" s="3" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
@@ -1917,6 +1974,9 @@
       <c r="D76" s="1">
         <v>5</v>
       </c>
+      <c r="F76" s="3" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
@@ -1931,6 +1991,9 @@
       <c r="D77" s="1">
         <v>5</v>
       </c>
+      <c r="F77" s="3" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
@@ -1945,6 +2008,9 @@
       <c r="D78" s="1">
         <v>5</v>
       </c>
+      <c r="F78" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
@@ -1959,6 +2025,9 @@
       <c r="D79" s="1">
         <v>5</v>
       </c>
+      <c r="F79" s="3" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
@@ -1973,8 +2042,11 @@
       <c r="D80" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F80" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>103</v>
       </c>
@@ -1987,8 +2059,11 @@
       <c r="D81" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F81" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>104</v>
       </c>
@@ -2000,6 +2075,9 @@
       </c>
       <c r="D82" s="1">
         <v>5</v>
+      </c>
+      <c r="F82" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/upload files/Requirements.xlsx
+++ b/upload files/Requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A22A4713-A78B-FD41-A609-C0DB4029FF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA85BCF-91F0-F148-8074-BC42422DF14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="14720" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3920" yWindow="660" windowWidth="21360" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
